--- a/data/price tracker_swiss_2026 0912_v1.xlsx
+++ b/data/price tracker_swiss_2026 0912_v1.xlsx
@@ -10136,7 +10136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J101"/>
+  <dimension ref="A1:J77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="19.375" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -10447,11 +10447,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>QE43Q7FAAU</t>
+          <t>QE43QN90FAT</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>609</v>
+        <v>934</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -10474,11 +10474,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -10486,11 +10486,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>QE43QN90FAT</t>
+          <t>UE43M70HAUXXN</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>934</v>
+        <v>399</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -10517,7 +10517,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -10525,11 +10525,11 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UE43M70HAUXXN</t>
+          <t>UE43U8090HUXXN</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -10556,19 +10556,19 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>UE43U8090HUXXN</t>
+          <t>QE48S85HAEXXN</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>480</v>
+        <v>1346</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -10603,11 +10603,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>QE48S85HAEXXN</t>
+          <t>QE48S90HAEXZU</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1346</v>
+        <v>1139</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -10642,11 +10642,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>QE48S90HAEXZU</t>
+          <t>QE48S95HAEXZU</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1139</v>
+        <v>1919</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -10669,23 +10669,23 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>QE48S95HAEXZU</t>
+          <t>QE50LS03FA</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1919</v>
+        <v>832</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -10712,7 +10712,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -10720,11 +10720,11 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>QE50LS03FA</t>
+          <t>QE50Q8FAAU</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>832</v>
+        <v>449</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -10759,11 +10759,11 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>QE50Q7FAAU</t>
+          <t>QE50QN80FAU</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>779</v>
+        <v>699</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -10798,11 +10798,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>QE50Q8FAAU</t>
+          <t>QE50QN80HAUXXN</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>449</v>
+        <v>968</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>QE50QN80FAU</t>
+          <t>QE50QN90FAT</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -10868,7 +10868,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -10876,11 +10876,11 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>QE50QN80HAUXXN</t>
+          <t>UE50M70HAUXXN</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>968</v>
+        <v>449</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -10915,11 +10915,11 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>QE50QN90FAT</t>
+          <t>UE50U8000F</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>699</v>
+        <v>399</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -10954,11 +10954,11 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>UE50M70HAUXXN</t>
+          <t>UE50U8090HUXXN</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>449</v>
+        <v>442</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -10981,23 +10981,23 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UE50U8000F</t>
+          <t>MRE55R85HAUXXN</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -11024,19 +11024,19 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UE50U8090HUXXN</t>
+          <t>QE55LS03HWUXZU</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>442</v>
+        <v>2200</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -11048,7 +11048,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -11063,7 +11063,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -11071,11 +11071,11 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>MRE55R85HAUXXN</t>
+          <t>QE55Q7F2AUXXH</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1200</v>
+        <v>902</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -11087,7 +11087,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11098,11 +11098,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -11110,11 +11110,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>QE55LS03HWUXZU</t>
+          <t>QE55Q8FAAU</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>2200</v>
+        <v>459</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11149,11 +11149,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>QE55Q7F2AUXXH</t>
+          <t>QE55QN80HAUXXN</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>902</v>
+        <v>1078</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -11188,11 +11188,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>QE55Q8FAAU</t>
+          <t>QE55QN90FAT</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>459</v>
+        <v>799</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -11227,11 +11227,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>QE55QEF1AU</t>
+          <t>QE55S90FAE</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>1350</v>
+        <v>899</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -11254,11 +11254,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -11266,11 +11266,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>QE55QN70FAU</t>
+          <t>QE55S90HAEXZU</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>812</v>
+        <v>1315</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -11305,11 +11305,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>QE55QN80FAU</t>
+          <t>QE55S95F</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>1325</v>
+        <v>1933</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -11336,7 +11336,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -11344,11 +11344,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>QE55QN80HAUXXN</t>
+          <t>QE55S99HATXZU</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>1078</v>
+        <v>2000</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -11360,7 +11360,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -11371,11 +11371,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -11383,11 +11383,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>QE55QN90FAT</t>
+          <t>UE55M70HAUXXN</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>799</v>
+        <v>499</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -11410,11 +11410,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -11422,11 +11422,11 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>QE55S90FAE</t>
+          <t>UE55U8090HUXXN</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>899</v>
+        <v>450</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -11453,19 +11453,19 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>QE55S90HAEXZU</t>
+          <t>MRE65R85HAUXXN</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1315</v>
+        <v>1590</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -11492,19 +11492,19 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>QE55S95F</t>
+          <t>QE65LS03FA</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1933</v>
+        <v>1961</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -11516,7 +11516,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -11527,23 +11527,23 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>QE55S95HFTXZU</t>
+          <t>QE65LS03FW</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>3058</v>
+        <v>1599</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -11555,7 +11555,7 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -11570,19 +11570,19 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>QE55S99HATXZU</t>
+          <t>QE65LS03HAUXXN</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>2000</v>
+        <v>2499</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -11605,23 +11605,23 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>UE55M70HAUXXN</t>
+          <t>QE65Q7F5AU</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>499</v>
+        <v>967</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -11644,23 +11644,23 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>UE55U8070H</t>
+          <t>QE65Q8FAAU</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>862</v>
+        <v>649</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -11687,19 +11687,19 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>UE55U8090HUXXN</t>
+          <t>QE65QN80HAUXXN</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>450</v>
+        <v>1352</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -11722,11 +11722,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -11734,11 +11734,11 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>MRE65R85HAUXXN</t>
+          <t>QE65QN90FAT</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1590</v>
+        <v>1199</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -11773,11 +11773,11 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>MRE65R95HATXZU</t>
+          <t>QE65S85HAEXZU</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4278</v>
+        <v>1666</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -11812,11 +11812,11 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>QE65LS03FA</t>
+          <t>QE65S90FAT</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1961</v>
+        <v>1199</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -11828,7 +11828,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -11839,11 +11839,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -11851,11 +11851,11 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>QE65LS03FW</t>
+          <t>QE65S90HAE</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1599</v>
+        <v>1700</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -11882,7 +11882,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -11890,11 +11890,11 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>QE65LS03HAUXXN</t>
+          <t>QE65S95HFTXZU</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>2499</v>
+        <v>3400</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -11906,7 +11906,7 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -11917,11 +11917,11 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -11929,11 +11929,11 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>QE65Q7F5AU</t>
+          <t>QE65S99HATXZU</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>967</v>
+        <v>2600</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -11956,11 +11956,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -11968,11 +11968,11 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>QE65Q7FAAU</t>
+          <t>UE65M70HAU</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1013</v>
+        <v>599</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -12007,11 +12007,11 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>QE65Q8FAAU</t>
+          <t>UE65U8000F</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>649</v>
+        <v>549</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -12034,11 +12034,11 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -12046,11 +12046,11 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>QE65QN70FAU</t>
+          <t>UE65U8090HUXXN</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>943</v>
+        <v>700</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -12073,23 +12073,23 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>QE65QN80FAU</t>
+          <t>MRE75R85HAUXXN</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1559</v>
+        <v>1959</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -12112,23 +12112,23 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>QE65QN80HAUXXN</t>
+          <t>QE75LS03FW</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1352</v>
+        <v>3291</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -12151,23 +12151,23 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>QE65QN90FAT</t>
+          <t>QE75LS03HWUXZU</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1199</v>
+        <v>3268</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -12190,23 +12190,23 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>QE65S85HAEXZU</t>
+          <t>QE75Q7FAAU</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1666</v>
+        <v>1059</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12233,19 +12233,19 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>QE65S90FAT</t>
+          <t>QE75Q8FAAU</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>1199</v>
+        <v>849</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -12268,23 +12268,23 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>QE65S90HAE</t>
+          <t>QE75QN80FAU</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1700</v>
+        <v>2000</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -12296,7 +12296,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12307,23 +12307,23 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>QE65S95HFTXZU</t>
+          <t>QE75QN90FAT</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>3400</v>
+        <v>1699</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -12335,7 +12335,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12350,19 +12350,19 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>QE65S99HATXZU</t>
+          <t>UE75M70HAUXXN</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2600</v>
+        <v>899</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12389,19 +12389,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>UE65M70HAU</t>
+          <t>UE75U8090HUXXN</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>599</v>
+        <v>825</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -12428,19 +12428,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>UE65U8000F</t>
+          <t>QE77S90FAE</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>549</v>
+        <v>1799</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -12467,19 +12467,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>UE65U8070H</t>
+          <t>QE77S90HATXZU</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>1106</v>
+        <v>2500</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -12491,7 +12491,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -12502,23 +12502,23 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>UE65U8090HUXXN</t>
+          <t>QE77S95F</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>700</v>
+        <v>2565</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -12545,19 +12545,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>MRE75R85HAUXXN</t>
+          <t>QE77S95HFTXZU</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1959</v>
+        <v>4329</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -12584,19 +12584,19 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MRE75R95HATXZU</t>
+          <t>QE77S99HATXZU</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5498</v>
+        <v>3800</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -12623,19 +12623,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>QE75LS03FW</t>
+          <t>QE83S85F</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3291</v>
+        <v>1799</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -12662,19 +12662,19 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>QE75LS03HWUXZU</t>
+          <t>QE83S85HAEXZU</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>3268</v>
+        <v>3093</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -12686,7 +12686,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -12697,23 +12697,23 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>QE75Q7F5AU</t>
+          <t>QE83S90HAEXZU</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1637</v>
+        <v>3199</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -12740,19 +12740,19 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>QE75Q7FAAU</t>
+          <t>QE83S95F</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1059</v>
+        <v>4500</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -12775,23 +12775,23 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>QLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>QE75Q8FAAU</t>
+          <t>MRE85R85HAUXXN</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>849</v>
+        <v>2879</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
         </is>
       </c>
     </row>
@@ -12822,15 +12822,15 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>QE75QEF1AU</t>
+          <t>QE85LS03FW</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2326</v>
+        <v>3728</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -12842,7 +12842,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Frame Bezel &amp; Art Store Promotion</t>
         </is>
       </c>
     </row>
@@ -12861,15 +12861,15 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>QE75QN73F</t>
+          <t>QE85Q7FAAU</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>3180</v>
+        <v>1299</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -12900,15 +12900,15 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>QE75QN80FAU</t>
+          <t>QE85Q8FAAU</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>2000</v>
+        <v>1199</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -12939,15 +12939,15 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>QE75QN80HAUXXN</t>
+          <t>QE85QN70FAU</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2815</v>
+        <v>1399</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -12978,15 +12978,15 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>QE75QN90FAT</t>
+          <t>QE85QN80FAU</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1699</v>
+        <v>1889</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -13017,15 +13017,15 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>UE75M70HAUXXN</t>
+          <t>UE85M70HAUXXN</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>899</v>
+        <v>1099</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -13056,15 +13056,15 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>UE75U8000F</t>
+          <t>UE85U8000F</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1048</v>
+        <v>949</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -13095,15 +13095,15 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>UE75U8070HUXXN</t>
+          <t>UE85U8090HUXXN</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>1472</v>
+        <v>1100</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -13130,19 +13130,19 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>QLED</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>UE75U8090HUXXN</t>
+          <t>QE100QN80HUXZU</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>825</v>
+        <v>3299</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -13153,942 +13153,6 @@
         <v>0</v>
       </c>
       <c r="J77" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>77</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>QE77S85HAEXZU</t>
-        </is>
-      </c>
-      <c r="F78" t="n">
-        <v>3669</v>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>0</v>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>77</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>QE77S90FAE</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>1799</v>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>77</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>QE77S90HATXZU</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>2500</v>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>77</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>QE77S95F</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>2565</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>0</v>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>77</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>QE77S95HFTXZU</t>
-        </is>
-      </c>
-      <c r="F82" t="n">
-        <v>4329</v>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>0</v>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>77</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>QE77S99HATXZU</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>3800</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I83" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>83</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>QE83S85F</t>
-        </is>
-      </c>
-      <c r="F84" t="n">
-        <v>1799</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>0</v>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>83</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>QE83S85HAEXZU</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>3093</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I85" t="n">
-        <v>0</v>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>83</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>QE83S90FAE</t>
-        </is>
-      </c>
-      <c r="F86" t="n">
-        <v>3899</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I86" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>83</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>QE83S90HAEXZU</t>
-        </is>
-      </c>
-      <c r="F87" t="n">
-        <v>3199</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I87" t="n">
-        <v>0</v>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>83</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>QE83S95F</t>
-        </is>
-      </c>
-      <c r="F88" t="n">
-        <v>4500</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I88" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B89" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>83</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>QE83S99HAEXZU</t>
-        </is>
-      </c>
-      <c r="F89" t="n">
-        <v>6718</v>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B90" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>85</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>MRE85R85HAUXXN</t>
-        </is>
-      </c>
-      <c r="F90" t="n">
-        <v>2879</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I90" t="n">
-        <v>0</v>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>85</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>MRE85R95HATXZU</t>
-        </is>
-      </c>
-      <c r="F91" t="n">
-        <v>6718</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>0</v>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Free Music Studio 5 Soundbar (HW-LS50H/EN)</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>85</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>QE85LS03FW</t>
-        </is>
-      </c>
-      <c r="F92" t="n">
-        <v>3728</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I92" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>Free Frame Bezel &amp; Art Store Promotion</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>QLED</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>85</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>QE85Q7FAAU</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>1299</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>QLED</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>85</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>QE85Q8FAAU</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>1199</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>QLED</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>85</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>QE85QN70FAU</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>1399</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>QLED</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>85</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>QE85QN80FAU</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>1889</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>QLED</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>85</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>QE85QN80HAUXXN</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>2448</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>85</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>UE85M70HAUXXN</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>1099</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>UHD 4K</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>85</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>UE85U8000F</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>949</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>UHD 4K</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>85</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>UE85U8090HUXXN</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>1100</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Samsung</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>QLED</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>100</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>QE100QN80HUXZU</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>3299</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="inlineStr">
         <is>
           <t>None</t>
         </is>
@@ -14113,7 +13177,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J111"/>
+  <dimension ref="A1:J92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16.5"/>
   <cols>
     <col width="14.5" bestFit="1" customWidth="1" min="3" max="3"/>
@@ -14413,11 +13477,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -14425,11 +13489,11 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>43QNED86B6B</t>
+          <t>43UA73006LA</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>862</v>
+        <v>437</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -14464,11 +13528,11 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>43UA73006LA</t>
+          <t>43UA75006LA</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>437</v>
+        <v>455</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -14491,23 +13555,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>43UA75006LA</t>
+          <t>OLED48B68LA</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>455</v>
+        <v>1099</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -14519,7 +13583,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -14530,7 +13594,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -14542,11 +13606,11 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>OLED48B68LA</t>
+          <t>OLED48C57LA</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1099</v>
+        <v>880</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -14558,7 +13622,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14581,11 +13645,11 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>OLED48C57LA</t>
+          <t>OLED48C58LA</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>880</v>
+        <v>839</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -14620,11 +13684,11 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>OLED48C58LA</t>
+          <t>OLED48C5ELB</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>839</v>
+        <v>849</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -14647,7 +13711,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -14659,11 +13723,11 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>OLED48C5ELB</t>
+          <t>OLED48C6ELB</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>849</v>
+        <v>1399</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -14675,7 +13739,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -14690,19 +13754,19 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>OLED48C67LA</t>
+          <t>50NU800B6LC</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1716</v>
+        <v>411</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -14714,7 +13778,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14729,19 +13793,19 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>OLED48C6ELB</t>
+          <t>50QNED70B6C</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1399</v>
+        <v>449</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -14753,7 +13817,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14764,11 +13828,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -14776,11 +13840,11 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>50MRGB87B9B</t>
+          <t>50QNED80A6A</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1350</v>
+        <v>480</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -14792,7 +13856,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -14807,7 +13871,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -14815,11 +13879,11 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>50NANO80A6B</t>
+          <t>50QNED86A6C</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>801</v>
+        <v>499</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -14846,19 +13910,19 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>50NU800B6LC</t>
+          <t>55LX7B6LA</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>411</v>
+        <v>1099</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -14885,19 +13949,19 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>50QNED70B6C</t>
+          <t>55MRGB87B9B</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>449</v>
+        <v>999</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -14909,7 +13973,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
         </is>
       </c>
     </row>
@@ -14924,19 +13988,19 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>50QNED80A6A</t>
+          <t>55NANO80A6B</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>480</v>
+        <v>389</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -14963,19 +14027,19 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>50QNED86A6C</t>
+          <t>55NANO81A3A</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>499</v>
+        <v>330</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -14998,23 +14062,23 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>50QNED87A6D.AEU</t>
+          <t>55NU800B6LA</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1472</v>
+        <v>398</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -15041,19 +14105,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>50UA75006LA</t>
+          <t>55QNED70A6A</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>492</v>
+        <v>379</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -15080,7 +14144,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -15088,11 +14152,11 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>55LX7B6LA</t>
+          <t>55QNED83B6A</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>1099</v>
+        <v>642</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -15115,11 +14179,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -15127,11 +14191,11 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>55MRGB87B9B</t>
+          <t>55QNED86A6A</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>999</v>
+        <v>519</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -15143,7 +14207,7 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15158,7 +14222,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -15166,11 +14230,11 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>55NANO80A6B</t>
+          <t>55QNED93A6A</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>389</v>
+        <v>687</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -15197,7 +14261,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -15205,11 +14269,11 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>55NANO81A3A</t>
+          <t>55UA73003LA</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>330</v>
+        <v>307</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -15232,7 +14296,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -15244,11 +14308,11 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>55NU800B6LA</t>
+          <t>55UA75006LA</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -15271,11 +14335,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -15283,11 +14347,11 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>55QNED70A6A</t>
+          <t>OLED55B68LA</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>379</v>
+        <v>1299</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -15299,7 +14363,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15314,7 +14378,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -15322,11 +14386,11 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>55QNED80A6A</t>
+          <t>OLED55C57LA</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>701</v>
+        <v>949</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -15349,11 +14413,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -15361,11 +14425,11 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>55QNED83B6A</t>
+          <t>OLED55C58LA</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>642</v>
+        <v>949</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -15392,7 +14456,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -15400,11 +14464,11 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>55QNED86A6A</t>
+          <t>OLED55C5ELB</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>519</v>
+        <v>1112</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -15431,7 +14495,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -15439,11 +14503,11 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>55QNED87B6A</t>
+          <t>OLED55C6ELB</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1472</v>
+        <v>1599</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -15455,7 +14519,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15470,7 +14534,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -15478,11 +14542,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>55QNED93A6A</t>
+          <t>OLED55G56LS</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>687</v>
+        <v>1034</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -15509,7 +14573,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -15517,11 +14581,11 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>55UA73003LA</t>
+          <t>OLED55G57LW</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>307</v>
+        <v>1399</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -15548,7 +14612,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -15556,11 +14620,11 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>55UA75006LA</t>
+          <t>OLED55G58LW</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>400</v>
+        <v>1114</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -15583,7 +14647,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -15595,11 +14659,11 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>OLED55B68LA</t>
+          <t>OLED55G59LS</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1299</v>
+        <v>1177</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -15611,7 +14675,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15622,7 +14686,7 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -15634,11 +14698,11 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>OLED55C57LA</t>
+          <t>OLED55G67LW</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>949</v>
+        <v>2599</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -15650,7 +14714,7 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15661,7 +14725,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -15673,11 +14737,11 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>OLED55C58LA</t>
+          <t>OLED55G69LS</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>949</v>
+        <v>2449</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -15689,7 +14753,7 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -15700,23 +14764,23 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>OLED55C5ELB</t>
+          <t>65LX7B6LA</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1112</v>
+        <v>1299</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -15743,19 +14807,19 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>OLED55C67LA</t>
+          <t>65MRGB87B9B</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1838</v>
+        <v>1200</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -15767,7 +14831,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
         </is>
       </c>
     </row>
@@ -15778,23 +14842,23 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>OLED55C6ELB</t>
+          <t>65NANO81A3A</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1599</v>
+        <v>810</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -15806,7 +14870,7 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -15817,23 +14881,23 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>OLED55G56LS</t>
+          <t>65NU800B6LA</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1034</v>
+        <v>527</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -15860,19 +14924,19 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>OLED55G57LW</t>
+          <t>65QNED80A6A</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>1399</v>
+        <v>599</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -15899,19 +14963,19 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>OLED55G58LW</t>
+          <t>65QNED86A6A</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>1114</v>
+        <v>699</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -15938,19 +15002,19 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>OLED55G59LS</t>
+          <t>65QNED87A6B.AEU</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>1177</v>
+        <v>999</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -15973,7 +15037,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -15981,15 +15045,15 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>OLED55G67LW</t>
+          <t>OLED65B59LA</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>2599</v>
+        <v>1049</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -16001,7 +15065,7 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16020,15 +15084,15 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OLED55G69LS</t>
+          <t>OLED65B68LA</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>2449</v>
+        <v>1799</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -16051,11 +15115,11 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -16063,11 +15127,11 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>65LX7B6LA</t>
+          <t>OLED65C57LA</t>
         </is>
       </c>
       <c r="F50" t="n">
-        <v>1299</v>
+        <v>1249</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -16090,11 +15154,11 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -16102,11 +15166,11 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>65MRGB87B9B</t>
+          <t>OLED65C59LB</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>1200</v>
+        <v>1230</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -16118,7 +15182,7 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16129,11 +15193,11 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -16141,11 +15205,11 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>65NANO80A6B</t>
+          <t>OLED65C67LA</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1106</v>
+        <v>1999</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -16157,7 +15221,7 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16168,11 +15232,11 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -16180,11 +15244,11 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>65NANO81A3A</t>
+          <t>OLED65C6ELB</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>810</v>
+        <v>1999</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -16196,7 +15260,7 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16207,11 +15271,11 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -16219,11 +15283,11 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>65NU800B6LA</t>
+          <t>OLED65G59LS</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>527</v>
+        <v>1800</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -16246,11 +15310,11 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -16258,11 +15322,11 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>65QNED80A6A</t>
+          <t>OLED65G67LW</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>599</v>
+        <v>3359</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -16274,7 +15338,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16285,11 +15349,11 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -16297,11 +15361,11 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>65QNED86A6A</t>
+          <t>OLED65G69LS</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>699</v>
+        <v>3499</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -16313,7 +15377,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16324,23 +15388,23 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>65QNED87A6B.AEU</t>
+          <t>75MRGB87B9B</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>999</v>
+        <v>1629</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -16352,7 +15416,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
         </is>
       </c>
     </row>
@@ -16367,19 +15431,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>65QNED87B6A</t>
+          <t>75MRGB96B9B</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1716</v>
+        <v>4299</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -16391,7 +15455,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
         </is>
       </c>
     </row>
@@ -16406,19 +15470,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>65QNED93A6A</t>
+          <t>75NANO80A6B</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>2448</v>
+        <v>777</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -16445,19 +15509,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>65UA75006LA</t>
+          <t>75NANO81A3A</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>662</v>
+        <v>1114</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -16480,23 +15544,23 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>OLED65B59LA</t>
+          <t>75NU800B6LA</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1049</v>
+        <v>685</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -16523,19 +15587,19 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>OLED65B68LA</t>
+          <t>75QNED70B6A</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1799</v>
+        <v>1030</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -16547,7 +15611,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16558,23 +15622,23 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>OLED65C57LA</t>
+          <t>75QNED7EB3A</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1249</v>
+        <v>693</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -16601,19 +15665,19 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>OLED65C59LB</t>
+          <t>75QNED80A3A</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>1230</v>
+        <v>1053</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -16636,23 +15700,23 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>OLED65C67LA</t>
+          <t>75QNED80A6A</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1999</v>
+        <v>899</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -16664,7 +15728,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16675,23 +15739,23 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>OLED65C6ELB</t>
+          <t>75UA75006LA</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1999</v>
+        <v>666</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -16703,7 +15767,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16722,15 +15786,15 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>OLED65G59LS</t>
+          <t>OLED77B59LA</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1800</v>
+        <v>1669</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -16761,15 +15825,15 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>OLED65G67LW</t>
+          <t>OLED77B68LA</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>3359</v>
+        <v>2499</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -16792,7 +15856,7 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -16800,15 +15864,15 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>OLED65G69LS</t>
+          <t>OLED77C55LA</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>3499</v>
+        <v>1764</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -16820,7 +15884,7 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16831,23 +15895,23 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>75MRGB87B9B</t>
+          <t>OLED77C57LA</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1629</v>
+        <v>1891</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -16859,7 +15923,7 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16870,23 +15934,23 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>75MRGB96B9B</t>
+          <t>OLED77C58LA</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>4299</v>
+        <v>1799</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -16898,7 +15962,7 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -16909,23 +15973,23 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>75NANO80A6B</t>
+          <t>OLED77C6ELB</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>777</v>
+        <v>2499</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -16937,7 +16001,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -16952,19 +16016,19 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>75NANO81A3A</t>
+          <t>OLED77G58LW</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>1114</v>
+        <v>2999</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -16991,19 +16055,19 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>75NU800B6LA</t>
+          <t>OLED77G67LW</t>
         </is>
       </c>
       <c r="F74" t="n">
-        <v>685</v>
+        <v>4999</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -17015,7 +16079,7 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17026,23 +16090,23 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>75QNED70B6A</t>
+          <t>OLED83B59LA</t>
         </is>
       </c>
       <c r="F75" t="n">
-        <v>1030</v>
+        <v>1789</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -17069,19 +16133,19 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>75QNED7EB3A</t>
+          <t>OLED83B68LA</t>
         </is>
       </c>
       <c r="F76" t="n">
-        <v>693</v>
+        <v>2999</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -17093,7 +16157,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17104,23 +16168,23 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>75QNED80A3A</t>
+          <t>OLED83B6ELB</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>1053</v>
+        <v>2999</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -17132,7 +16196,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17147,19 +16211,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>75QNED80A6A</t>
+          <t>OLED83C57LA</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>899</v>
+        <v>2163</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -17186,19 +16250,19 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>75QNED87A6B</t>
+          <t>OLED83C5ELA</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2936</v>
+        <v>2036</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -17225,19 +16289,19 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>QNED</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>75QNED87B6A</t>
+          <t>OLED83C67LA</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>2448</v>
+        <v>3499</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -17249,7 +16313,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17260,23 +16324,23 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>UHD 4K</t>
+          <t>OLED</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>75UA75006LA</t>
+          <t>OLED83C6ELB</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>666</v>
+        <v>3499</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -17288,7 +16352,7 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
         </is>
       </c>
     </row>
@@ -17307,15 +16371,15 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>OLED77B59LA</t>
+          <t>OLED83G57LW</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1669</v>
+        <v>3699</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -17346,15 +16410,15 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>OLED77B68LA</t>
+          <t>OLED83G67LW</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2499</v>
+        <v>5999</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -17377,23 +16441,23 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>UHD 4K</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>OLED77C55LA</t>
+          <t>85NU800B6LA</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>1764</v>
+        <v>873</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -17416,23 +16480,23 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>OLED77C57LA</t>
+          <t>85QNED70B6A</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1891</v>
+        <v>1829</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -17455,23 +16519,23 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>OLED77C58LA</t>
+          <t>85QNED7EB3A</t>
         </is>
       </c>
       <c r="F86" t="n">
-        <v>1799</v>
+        <v>959</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -17498,19 +16562,19 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>OLED77C67LA</t>
+          <t>86MRGB87B9B</t>
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3058</v>
+        <v>1999</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -17522,7 +16586,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
         </is>
       </c>
     </row>
@@ -17533,23 +16597,23 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>OLED77C6ELB</t>
+          <t>86NANO81A6A</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>2499</v>
+        <v>869</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -17561,7 +16625,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17576,19 +16640,19 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>OLED77G58LW</t>
+          <t>86QNED80A6A</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>2999</v>
+        <v>1199</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -17611,23 +16675,23 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>OLED77G67LW</t>
+          <t>86QNED86A6A</t>
         </is>
       </c>
       <c r="F90" t="n">
-        <v>4999</v>
+        <v>1199</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -17639,7 +16703,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -17650,23 +16714,23 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>OLED83B59LA</t>
+          <t>86QNED86B6B</t>
         </is>
       </c>
       <c r="F91" t="n">
-        <v>1789</v>
+        <v>1661</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -17689,23 +16753,23 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OLED</t>
+          <t>QNED</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>OLED83B68LA</t>
+          <t>100QNED86A6</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>2999</v>
+        <v>2111</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -17716,747 +16780,6 @@
         <v>0</v>
       </c>
       <c r="J92" t="inlineStr">
-        <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B93" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>83</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>OLED83B6ELB</t>
-        </is>
-      </c>
-      <c r="F93" t="n">
-        <v>2999</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>0</v>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B94" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>83</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>OLED83C57LA</t>
-        </is>
-      </c>
-      <c r="F94" t="n">
-        <v>2163</v>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I94" t="n">
-        <v>0</v>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B95" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>83</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>OLED83C59LB</t>
-        </is>
-      </c>
-      <c r="F95" t="n">
-        <v>5700</v>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I95" t="n">
-        <v>0</v>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B96" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>83</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>OLED83C5ELA</t>
-        </is>
-      </c>
-      <c r="F96" t="n">
-        <v>2036</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>0</v>
-      </c>
-      <c r="J96" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>83</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>OLED83C67LA</t>
-        </is>
-      </c>
-      <c r="F97" t="n">
-        <v>3499</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" t="inlineStr">
-        <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>83</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>OLED83C6ELB</t>
-        </is>
-      </c>
-      <c r="F98" t="n">
-        <v>3499</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I98" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" t="inlineStr">
-        <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B99" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>83</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>OLED83G57LW</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>3699</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I99" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>OLED</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>83</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>OLED83G67LW</t>
-        </is>
-      </c>
-      <c r="F100" t="n">
-        <v>5999</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Free SoundSuite/Soundbar with LG OLED TV 2026 Purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>UHD 4K</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>85</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>85NU800B6LA</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>873</v>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B102" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>85</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>85QNED70B6A</t>
-        </is>
-      </c>
-      <c r="F102" t="n">
-        <v>1829</v>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B103" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>85</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>85QNED7EB3A</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>959</v>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B104" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>86</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>86MRGB87B9B</t>
-        </is>
-      </c>
-      <c r="F104" t="n">
-        <v>1999</v>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" t="inlineStr">
-        <is>
-          <t>Free Premium Sound Suite with LG Micro RGB Purchase</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B105" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>LED</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>86</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>86NANO81A6A</t>
-        </is>
-      </c>
-      <c r="F105" t="n">
-        <v>869</v>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B106" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>86</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>86QNED80A6A</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>1199</v>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B107" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>86</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>86QNED86A6A</t>
-        </is>
-      </c>
-      <c r="F107" t="n">
-        <v>1199</v>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B108" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>86</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>86QNED86B6B</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>1661</v>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B109" t="n">
-        <v>2026</v>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>86</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>86QNED87B6A</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>3058</v>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B110" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>UHD 4K</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>86</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>86UA75006LA</t>
-        </is>
-      </c>
-      <c r="F110" t="n">
-        <v>1403</v>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>LG</t>
-        </is>
-      </c>
-      <c r="B111" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>QNED</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>100</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>100QNED86A6</t>
-        </is>
-      </c>
-      <c r="F111" t="n">
-        <v>2111</v>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="I111" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" t="inlineStr">
         <is>
           <t>None</t>
         </is>
